--- a/diseases/d088/2015-2019.xlsx
+++ b/diseases/d088/2015-2019.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
@@ -785,7 +790,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -796,6 +806,11 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -818,22 +833,22 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -860,17 +875,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -911,7 +926,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -919,6 +959,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -926,55 +1024,65 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1114,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1147,12 +1255,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1288,12 +1396,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1429,12 +1537,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1570,12 +1678,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1711,12 +1819,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1852,12 +1960,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1993,12 +2101,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2134,12 +2242,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2275,12 +2383,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2416,12 +2524,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2557,12 +2665,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2698,12 +2806,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2839,12 +2947,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2980,12 +3088,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3121,12 +3229,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3262,12 +3370,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3301,10 +3409,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3403,12 +3511,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3442,10 +3550,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3544,12 +3652,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3574,12 +3682,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3588,12 +3696,9 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3613,7 +3718,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AT22" t="n">
@@ -3621,42 +3726,42 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3793,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3732,9 +3837,17 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3749,55 +3862,65 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT23" t="n">
         <v>1</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3824,17 +3947,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3875,7 +3998,32 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3883,6 +4031,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN24" t="b">
+        <v>1</v>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3890,55 +4096,65 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT24" t="n">
         <v>1</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3970,12 +4186,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4111,12 +4327,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4252,12 +4468,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4393,12 +4609,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4534,12 +4750,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4675,12 +4891,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4816,12 +5032,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4957,12 +5173,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5098,12 +5314,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5239,12 +5455,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5380,12 +5596,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5521,12 +5737,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5662,12 +5878,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5803,12 +6019,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5944,12 +6160,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6085,12 +6301,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6226,12 +6442,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6367,12 +6583,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6397,12 +6613,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6411,12 +6627,9 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6436,7 +6649,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -6444,42 +6657,42 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6511,12 +6724,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6541,12 +6754,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6652,12 +6865,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6696,9 +6909,17 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6713,55 +6934,65 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
         <v>1</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6788,17 +7019,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6839,7 +7070,32 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6847,6 +7103,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -6854,55 +7168,65 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
         <v>1</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6934,12 +7258,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7075,12 +7399,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7216,12 +7540,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7357,12 +7681,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7498,12 +7822,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7639,12 +7963,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7780,12 +8104,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7921,12 +8245,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8062,12 +8386,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8203,12 +8527,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8344,12 +8668,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8485,12 +8809,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8626,12 +8950,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8767,12 +9091,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8908,12 +9232,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9049,12 +9373,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9190,12 +9514,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9220,12 +9544,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9234,12 +9558,9 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9259,7 +9580,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -9267,42 +9588,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9334,12 +9655,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9364,12 +9685,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -9475,12 +9796,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9505,12 +9826,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -9616,12 +9937,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9660,9 +9981,17 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9677,55 +10006,65 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT65" t="n">
         <v>1</v>
       </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9752,17 +10091,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9803,7 +10142,32 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9811,6 +10175,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN66" t="b">
+        <v>1</v>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9818,55 +10240,65 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT66" t="n">
         <v>1</v>
       </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9898,12 +10330,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10039,12 +10471,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10180,12 +10612,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10321,12 +10753,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10462,12 +10894,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10603,12 +11035,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10744,12 +11176,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10885,12 +11317,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11026,12 +11458,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11167,12 +11599,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11308,12 +11740,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11449,12 +11881,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11590,12 +12022,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11731,12 +12163,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11770,10 +12202,10 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -11872,12 +12304,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12013,12 +12445,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12043,12 +12475,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12057,12 +12489,9 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12082,7 +12511,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -12090,42 +12519,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12157,12 +12586,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12187,12 +12616,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -12298,12 +12727,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12328,19 +12757,19 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -12439,12 +12868,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12469,12 +12898,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -12580,12 +13009,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12624,9 +13053,17 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12641,55 +13078,65 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT86" t="n">
         <v>1</v>
       </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -12716,17 +13163,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12767,7 +13214,32 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12775,6 +13247,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -12782,55 +13312,65 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT87" t="n">
         <v>1</v>
       </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -12862,12 +13402,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13003,12 +13543,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13144,12 +13684,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13285,12 +13825,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13426,12 +13966,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13567,12 +14107,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13708,12 +14248,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -13849,12 +14389,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -13990,12 +14530,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14131,12 +14671,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -14272,12 +14812,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -14413,12 +14953,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -14554,12 +15094,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -14695,12 +15235,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -14803,6 +15343,711 @@
         </is>
       </c>
       <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NZ-WAI</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Wairarapa, New Zealand</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>NZ-WCT</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>West Coast, New Zealand</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NZ-WHG</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Whanganui, New Zealand</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>NZ-WKO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Waikato, New Zealand</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>NZ-WMT</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Waitemata, New Zealand</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -14934,7 +16179,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
@@ -14954,7 +16199,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -14964,7 +16209,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
